--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.99950999021656</v>
+        <v>9.587420373410191</v>
       </c>
       <c r="D2" t="n">
-        <v>58.91778311194388</v>
+        <v>9.574139755690881</v>
       </c>
       <c r="E2" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F2" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.2746959734574</v>
+        <v>7.682138095686827</v>
       </c>
       <c r="D3" t="n">
-        <v>47.21250688649183</v>
+        <v>7.672032369054922</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F3" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.40822499349093</v>
+        <v>9.491336561442276</v>
       </c>
       <c r="D4" t="n">
-        <v>58.38122624660559</v>
+        <v>9.48694926507341</v>
       </c>
       <c r="E4" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F4" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.9207308165219</v>
+        <v>6.487118757684808</v>
       </c>
       <c r="D5" t="n">
-        <v>39.8184738159107</v>
+        <v>6.470501995085489</v>
       </c>
       <c r="E5" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F5" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.93429787633533</v>
+        <v>7.139323404904491</v>
       </c>
       <c r="D6" t="n">
-        <v>43.83140684159996</v>
+        <v>7.122603611759994</v>
       </c>
       <c r="E6" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F6" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.60422965034587</v>
+        <v>4.485687318181204</v>
       </c>
       <c r="D7" t="n">
-        <v>27.49419392232327</v>
+        <v>4.467806512377531</v>
       </c>
       <c r="E7" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F7" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.78543261068811</v>
+        <v>7.602632799236819</v>
       </c>
       <c r="D8" t="n">
-        <v>46.78602310054215</v>
+        <v>7.602728753838099</v>
       </c>
       <c r="E8" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F8" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.2662470008506</v>
+        <v>8.818265137638223</v>
       </c>
       <c r="D9" t="n">
-        <v>54.17453359884036</v>
+        <v>8.803361709811558</v>
       </c>
       <c r="E9" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F9" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.65985086761629</v>
+        <v>4.169725765987647</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62946306026797</v>
+        <v>4.164787747293545</v>
       </c>
       <c r="E10" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F10" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.36588829753694</v>
+        <v>2.171956848349753</v>
       </c>
       <c r="D11" t="n">
-        <v>13.27491480371448</v>
+        <v>2.157173655603604</v>
       </c>
       <c r="E11" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F11" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.82299464987497</v>
+        <v>5.333736630604683</v>
       </c>
       <c r="D12" t="n">
-        <v>32.72814825048724</v>
+        <v>5.318324090704177</v>
       </c>
       <c r="E12" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F12" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.95058877502048</v>
+        <v>1.941970675940828</v>
       </c>
       <c r="D13" t="n">
-        <v>11.8796196231342</v>
+        <v>1.930438188759307</v>
       </c>
       <c r="E13" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F13" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.30826055033975</v>
+        <v>3.13759233943021</v>
       </c>
       <c r="D14" t="n">
-        <v>19.38156835641617</v>
+        <v>3.149504857917627</v>
       </c>
       <c r="E14" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F14" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.62526309272205</v>
+        <v>5.951605252567333</v>
       </c>
       <c r="D15" t="n">
-        <v>36.69388178486983</v>
+        <v>5.962755790041347</v>
       </c>
       <c r="E15" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F15" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.84284518708615</v>
+        <v>2.7369623429015</v>
       </c>
       <c r="D16" t="n">
-        <v>16.81620051613488</v>
+        <v>2.732632583871918</v>
       </c>
       <c r="E16" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F16" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>51.38992406761534</v>
+        <v>8.350862660987493</v>
       </c>
       <c r="D17" t="n">
-        <v>51.46283669612784</v>
+        <v>8.362710963120774</v>
       </c>
       <c r="E17" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F17" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>15.55721141772878</v>
+        <v>2.528046855380926</v>
       </c>
       <c r="D18" t="n">
-        <v>15.60179971741624</v>
+        <v>2.535292454080139</v>
       </c>
       <c r="E18" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F18" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>46.69091389178982</v>
+        <v>7.587273507415846</v>
       </c>
       <c r="D19" t="n">
-        <v>46.7828621732993</v>
+        <v>7.602215103161137</v>
       </c>
       <c r="E19" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F19" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.36937023326691</v>
+        <v>4.447522662905873</v>
       </c>
       <c r="D20" t="n">
-        <v>27.47512942684026</v>
+        <v>4.464708531861542</v>
       </c>
       <c r="E20" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F20" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>47.88997890592411</v>
+        <v>7.782121572212668</v>
       </c>
       <c r="D21" t="n">
-        <v>47.8956815629962</v>
+        <v>7.783048253986883</v>
       </c>
       <c r="E21" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F21" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>30.53499028766203</v>
+        <v>4.961935921745081</v>
       </c>
       <c r="D22" t="n">
-        <v>30.58668516562243</v>
+        <v>4.970336339413645</v>
       </c>
       <c r="E22" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F22" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>50.44148614085982</v>
+        <v>8.19674149788972</v>
       </c>
       <c r="D23" t="n">
-        <v>50.54574460535603</v>
+        <v>8.213683498370354</v>
       </c>
       <c r="E23" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F23" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>44.37082152229492</v>
+        <v>7.210258497372926</v>
       </c>
       <c r="D24" t="n">
-        <v>44.47982947228961</v>
+        <v>7.227972289247061</v>
       </c>
       <c r="E24" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F24" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>61.38344972889134</v>
+        <v>9.974810580944842</v>
       </c>
       <c r="D25" t="n">
-        <v>61.39603680802555</v>
+        <v>9.976855981304151</v>
       </c>
       <c r="E25" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F25" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>46.97953597991174</v>
+        <v>7.634174596735659</v>
       </c>
       <c r="D26" t="n">
-        <v>47.01927180921874</v>
+        <v>7.640631668998044</v>
       </c>
       <c r="E26" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F26" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>44.46055935684096</v>
+        <v>7.224840895486656</v>
       </c>
       <c r="D27" t="n">
-        <v>44.52227905728564</v>
+        <v>7.234870346808917</v>
       </c>
       <c r="E27" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F27" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>58.43841325832292</v>
+        <v>9.496242154477475</v>
       </c>
       <c r="D28" t="n">
-        <v>58.4662833321691</v>
+        <v>9.50077104147748</v>
       </c>
       <c r="E28" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F28" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>41.34079068566099</v>
+        <v>6.717878486419911</v>
       </c>
       <c r="D29" t="n">
-        <v>41.44874089069074</v>
+        <v>6.735420394737246</v>
       </c>
       <c r="E29" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F29" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>56.02435275980739</v>
+        <v>9.1039573234687</v>
       </c>
       <c r="D30" t="n">
-        <v>56.13459354731825</v>
+        <v>9.121871451439217</v>
       </c>
       <c r="E30" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F30" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>72.01912680834174</v>
+        <v>11.70310810635553</v>
       </c>
       <c r="D31" t="n">
-        <v>72.04230074131748</v>
+        <v>11.70687387046409</v>
       </c>
       <c r="E31" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F31" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>74.51263103769206</v>
+        <v>12.10830254362496</v>
       </c>
       <c r="D32" t="n">
-        <v>74.55417252786927</v>
+        <v>12.11505303577876</v>
       </c>
       <c r="E32" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F32" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>65.65197125100235</v>
+        <v>10.66844532828788</v>
       </c>
       <c r="D33" t="n">
-        <v>65.71811258537755</v>
+        <v>10.67919329512385</v>
       </c>
       <c r="E33" t="n">
-        <v>16.64353807016873</v>
+        <v>2.704574936402418</v>
       </c>
       <c r="F33" t="n">
-        <v>16.65854499138494</v>
+        <v>2.707013561100053</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
